--- a/Data/National Accounts/PSA-Quarter-Indicators-Derived.xlsx
+++ b/Data/National Accounts/PSA-Quarter-Indicators-Derived.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\Derived indicators\2023-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDAB23A-25BC-4722-964B-8342F6AD7E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71870E75-E792-4334-917E-3EF1112295CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Quarterly 2000-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Quarterly series" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Quarterly 2000-2025'!$A$1:$DB$61</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Quarterly 2000-2025'!$A:$A</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Quarterly series'!$A$1:$DB$61</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Quarterly series'!$A:$A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="48">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -186,7 +186,7 @@
     <t>16. Debt Service to GDP (in percent, current)</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
   </si>
 </sst>
 </file>
@@ -676,14 +676,14 @@
     <col min="1" max="1" width="53.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="81" width="12.140625" style="1" customWidth="1"/>
     <col min="82" max="82" width="10.42578125" style="1" customWidth="1"/>
-    <col min="83" max="85" width="9.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="87" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="84" max="87" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="88" max="89" width="9.28515625" style="1" customWidth="1"/>
-    <col min="90" max="90" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="91" max="91" width="9.5703125" style="1" customWidth="1"/>
-    <col min="92" max="105" width="11.7109375" style="1" customWidth="1"/>
-    <col min="106" max="106" width="1.28515625" style="1" customWidth="1"/>
-    <col min="107" max="16384" width="8.85546875" style="1"/>
+    <col min="92" max="106" width="11.7109375" style="1" customWidth="1"/>
+    <col min="107" max="107" width="1.28515625" style="1" customWidth="1"/>
+    <col min="108" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:115" x14ac:dyDescent="0.2">
@@ -867,6 +867,9 @@
       <c r="CY7" s="4"/>
       <c r="CZ7" s="4"/>
       <c r="DA7" s="4"/>
+      <c r="DB7" s="4">
+        <v>2026</v>
+      </c>
     </row>
     <row r="8" spans="1:115" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -1183,6 +1186,9 @@
       </c>
       <c r="DA8" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="DB8" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:115" ht="7.15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1464,6 +1470,7 @@
       <c r="CY12" s="6"/>
       <c r="CZ12" s="6"/>
       <c r="DA12" s="6"/>
+      <c r="DB12" s="6"/>
     </row>
     <row r="13" spans="1:115" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
@@ -1781,7 +1788,9 @@
       <c r="DA13" s="24">
         <v>129545.41768185058</v>
       </c>
-      <c r="DB13" s="24"/>
+      <c r="DB13" s="24">
+        <v>115280.98027671364</v>
+      </c>
       <c r="DC13" s="23"/>
       <c r="DD13" s="23"/>
       <c r="DE13" s="23"/>
@@ -2108,7 +2117,9 @@
       <c r="DA14" s="24">
         <v>51144.701934701072</v>
       </c>
-      <c r="DB14" s="24"/>
+      <c r="DB14" s="24">
+        <v>50005.332420287552</v>
+      </c>
       <c r="DC14" s="23"/>
       <c r="DD14" s="23"/>
       <c r="DE14" s="23"/>
@@ -2435,7 +2446,9 @@
       <c r="DA15" s="24">
         <v>211454.62764378919</v>
       </c>
-      <c r="DB15" s="24"/>
+      <c r="DB15" s="24">
+        <v>184634.19543536505</v>
+      </c>
       <c r="DC15" s="23"/>
       <c r="DD15" s="23"/>
       <c r="DE15" s="23"/>
@@ -2762,7 +2775,9 @@
       <c r="DA16" s="24">
         <v>132951.40158534885</v>
       </c>
-      <c r="DB16" s="24"/>
+      <c r="DB16" s="24">
+        <v>114879.18436265347</v>
+      </c>
       <c r="DC16" s="23"/>
       <c r="DD16" s="23"/>
       <c r="DE16" s="23"/>
@@ -3200,7 +3215,9 @@
       <c r="DA18" s="21">
         <v>3.0740987719670727</v>
       </c>
-      <c r="DB18" s="21"/>
+      <c r="DB18" s="21">
+        <v>2.2203966087194829</v>
+      </c>
       <c r="DC18" s="23"/>
       <c r="DD18" s="23"/>
       <c r="DE18" s="23"/>
@@ -3519,7 +3536,9 @@
       <c r="DA19" s="21">
         <v>0.23899715912889974</v>
       </c>
-      <c r="DB19" s="21"/>
+      <c r="DB19" s="21">
+        <v>8.5947072578991879</v>
+      </c>
       <c r="DC19" s="23"/>
       <c r="DD19" s="23"/>
       <c r="DE19" s="23"/>
@@ -3838,7 +3857,9 @@
       <c r="DA20" s="21">
         <v>2.5010405611087805</v>
       </c>
-      <c r="DB20" s="21"/>
+      <c r="DB20" s="21">
+        <v>-1.297099504304569</v>
+      </c>
       <c r="DC20" s="23"/>
       <c r="DD20" s="23"/>
       <c r="DE20" s="23"/>
@@ -4157,7 +4178,9 @@
       <c r="DA21" s="21">
         <v>4.405692946259208</v>
       </c>
-      <c r="DB21" s="21"/>
+      <c r="DB21" s="21">
+        <v>1.2828606972052512</v>
+      </c>
       <c r="DC21" s="23"/>
       <c r="DD21" s="23"/>
       <c r="DE21" s="23"/>
@@ -4484,7 +4507,9 @@
       <c r="DA22" s="21">
         <v>243.15038258236632</v>
       </c>
-      <c r="DB22" s="21"/>
+      <c r="DB22" s="21">
+        <v>215.21792672804253</v>
+      </c>
       <c r="DC22" s="23"/>
       <c r="DD22" s="23"/>
       <c r="DE22" s="23"/>
@@ -4922,7 +4947,9 @@
       <c r="DA24" s="21">
         <v>7.672557373640175E-2</v>
       </c>
-      <c r="DB24" s="21"/>
+      <c r="DB24" s="21">
+        <v>-1.5261834002785923E-2</v>
+      </c>
       <c r="DC24" s="23"/>
       <c r="DD24" s="23"/>
       <c r="DE24" s="23"/>
@@ -5241,7 +5268,9 @@
       <c r="DA25" s="21">
         <v>-8.0931425207660501E-2</v>
       </c>
-      <c r="DB25" s="21"/>
+      <c r="DB25" s="21">
+        <v>-1.2975266651965077E-2</v>
+      </c>
       <c r="DC25" s="23"/>
       <c r="DD25" s="23"/>
       <c r="DE25" s="23"/>
@@ -5560,7 +5589,9 @@
       <c r="DA26" s="21">
         <v>2.6741357800842169</v>
       </c>
-      <c r="DB26" s="21"/>
+      <c r="DB26" s="21">
+        <v>2.4373287910651862</v>
+      </c>
       <c r="DC26" s="23"/>
       <c r="DD26" s="23"/>
       <c r="DE26" s="23"/>
@@ -5879,7 +5910,9 @@
       <c r="DA27" s="21">
         <v>1.3648644553626272</v>
       </c>
-      <c r="DB27" s="21"/>
+      <c r="DB27" s="21">
+        <v>0.56549383744462067</v>
+      </c>
       <c r="DC27" s="23"/>
       <c r="DD27" s="23"/>
       <c r="DE27" s="23"/>
@@ -6198,7 +6231,9 @@
       <c r="DA28" s="21">
         <v>4.0347943839755853</v>
       </c>
-      <c r="DB28" s="21"/>
+      <c r="DB28" s="21">
+        <v>2.9745855278550559</v>
+      </c>
       <c r="DC28" s="23"/>
       <c r="DD28" s="23"/>
       <c r="DE28" s="23"/>
@@ -6525,7 +6560,9 @@
       <c r="DA29" s="21">
         <v>95.616765408838233</v>
       </c>
-      <c r="DB29" s="21"/>
+      <c r="DB29" s="21">
+        <v>92.092599988048889</v>
+      </c>
       <c r="DC29" s="23"/>
       <c r="DD29" s="23"/>
       <c r="DE29" s="23"/>
@@ -6852,7 +6889,9 @@
       <c r="DA30" s="24">
         <v>-83639.682252578787</v>
       </c>
-      <c r="DB30" s="24"/>
+      <c r="DB30" s="24">
+        <v>-168301.46656140732</v>
+      </c>
       <c r="DC30" s="23"/>
       <c r="DD30" s="23"/>
       <c r="DE30" s="23"/>
@@ -7417,7 +7456,9 @@
       <c r="DA33" s="24">
         <v>-698922.68165097293</v>
       </c>
-      <c r="DB33" s="24"/>
+      <c r="DB33" s="24">
+        <v>-1043557.7610697476</v>
+      </c>
       <c r="DC33" s="23"/>
       <c r="DD33" s="23"/>
       <c r="DE33" s="23"/>
@@ -7744,7 +7785,9 @@
       <c r="DA34" s="21">
         <v>-8.8391342826583976</v>
       </c>
-      <c r="DB34" s="21"/>
+      <c r="DB34" s="21">
+        <v>-15.050015091023894</v>
+      </c>
       <c r="DC34" s="23"/>
       <c r="DD34" s="23"/>
       <c r="DE34" s="23"/>
@@ -8071,7 +8114,9 @@
       <c r="DA35" s="24">
         <v>-882048.01015851926</v>
       </c>
-      <c r="DB35" s="24"/>
+      <c r="DB35" s="24">
+        <v>-1473466.5096268314</v>
+      </c>
       <c r="DC35" s="23"/>
       <c r="DD35" s="23"/>
       <c r="DE35" s="23"/>
@@ -8398,7 +8443,9 @@
       <c r="DA36" s="21">
         <v>59.291292354329407</v>
       </c>
-      <c r="DB36" s="21"/>
+      <c r="DB36" s="21">
+        <v>74.695584594209649</v>
+      </c>
       <c r="DC36" s="23"/>
       <c r="DD36" s="23"/>
       <c r="DE36" s="23"/>
@@ -8844,7 +8891,9 @@
       <c r="DA38" s="21">
         <v>1994661.2692439985</v>
       </c>
-      <c r="DB38" s="21"/>
+      <c r="DB38" s="21">
+        <v>2067891.5134642548</v>
+      </c>
       <c r="DC38" s="23"/>
       <c r="DD38" s="23"/>
       <c r="DE38" s="23"/>
@@ -9171,7 +9220,9 @@
       <c r="DA39" s="24">
         <v>33989.695873942117</v>
       </c>
-      <c r="DB39" s="24"/>
+      <c r="DB39" s="24">
+        <v>35075.008401038009</v>
+      </c>
       <c r="DC39" s="23"/>
       <c r="DD39" s="23"/>
       <c r="DE39" s="23"/>
@@ -9498,7 +9549,9 @@
       <c r="DA40" s="21">
         <v>25.226079035835504</v>
       </c>
-      <c r="DB40" s="21"/>
+      <c r="DB40" s="21">
+        <v>29.822784751592877</v>
+      </c>
       <c r="DC40" s="23"/>
       <c r="DD40" s="23"/>
       <c r="DE40" s="23"/>
@@ -9944,7 +9997,9 @@
       <c r="DA42" s="24">
         <v>2693583.9508949714</v>
       </c>
-      <c r="DB42" s="24"/>
+      <c r="DB42" s="24">
+        <v>3111449.2745340024</v>
+      </c>
       <c r="DC42" s="23"/>
       <c r="DD42" s="23"/>
       <c r="DE42" s="23"/>
@@ -10271,7 +10326,9 @@
       <c r="DA43" s="24">
         <v>45899.572380302779</v>
       </c>
-      <c r="DB43" s="24"/>
+      <c r="DB43" s="24">
+        <v>52775.548781500533</v>
+      </c>
       <c r="DC43" s="23"/>
       <c r="DD43" s="23"/>
       <c r="DE43" s="23"/>
@@ -10598,7 +10655,9 @@
       <c r="DA44" s="21">
         <v>34.065213318493903</v>
       </c>
-      <c r="DB44" s="21"/>
+      <c r="DB44" s="21">
+        <v>44.872799842616772</v>
+      </c>
       <c r="DC44" s="23"/>
       <c r="DD44" s="23"/>
       <c r="DE44" s="23"/>
@@ -10925,7 +10984,9 @@
       <c r="DA45" s="21">
         <v>73.579288523048533</v>
       </c>
-      <c r="DB45" s="21"/>
+      <c r="DB45" s="21">
+        <v>68.800308885278739</v>
+      </c>
       <c r="DC45" s="23"/>
       <c r="DD45" s="23"/>
       <c r="DE45" s="23"/>
@@ -11252,7 +11313,9 @@
       <c r="DA46" s="21">
         <v>57.556202351993846</v>
       </c>
-      <c r="DB46" s="21"/>
+      <c r="DB46" s="21">
+        <v>63.291145286041854</v>
+      </c>
       <c r="DC46" s="23"/>
       <c r="DD46" s="23"/>
       <c r="DE46" s="23"/>
@@ -11579,7 +11642,9 @@
       <c r="DA47" s="21">
         <v>12.585050730438518</v>
       </c>
-      <c r="DB47" s="21"/>
+      <c r="DB47" s="21">
+        <v>12.785219598134709</v>
+      </c>
       <c r="DC47" s="23"/>
       <c r="DD47" s="23"/>
       <c r="DE47" s="23"/>
@@ -12025,7 +12090,9 @@
       <c r="DA49" s="24">
         <v>1174843.8020681022</v>
       </c>
-      <c r="DB49" s="24"/>
+      <c r="DB49" s="24">
+        <v>1092980.6419674195</v>
+      </c>
       <c r="DC49" s="23"/>
       <c r="DD49" s="23"/>
       <c r="DE49" s="23"/>
@@ -12352,7 +12419,9 @@
       <c r="DA50" s="24">
         <v>20019.731744636316</v>
       </c>
-      <c r="DB50" s="24"/>
+      <c r="DB50" s="24">
+        <v>18538.837724110534</v>
+      </c>
       <c r="DC50" s="23"/>
       <c r="DD50" s="23"/>
       <c r="DE50" s="23"/>
@@ -12671,7 +12740,9 @@
       <c r="DA51" s="21">
         <v>15.795836019971276</v>
       </c>
-      <c r="DB51" s="21"/>
+      <c r="DB51" s="21">
+        <v>7.4796034447768989</v>
+      </c>
       <c r="DC51" s="23"/>
       <c r="DD51" s="23"/>
       <c r="DE51" s="23"/>
@@ -12990,7 +13061,9 @@
       <c r="DA52" s="21">
         <v>14.741052973605306</v>
       </c>
-      <c r="DB52" s="21"/>
+      <c r="DB52" s="21">
+        <v>5.6839894556133288</v>
+      </c>
       <c r="DC52" s="23"/>
       <c r="DD52" s="23"/>
       <c r="DE52" s="23"/>
@@ -13317,7 +13390,9 @@
       <c r="DA53" s="21">
         <v>12.988124323379466</v>
       </c>
-      <c r="DB53" s="21"/>
+      <c r="DB53" s="21">
+        <v>13.747477096916441</v>
+      </c>
       <c r="DC53" s="23"/>
       <c r="DD53" s="23"/>
       <c r="DE53" s="23"/>
@@ -13644,7 +13719,9 @@
       <c r="DA54" s="21">
         <v>14.858012767733797</v>
       </c>
-      <c r="DB54" s="21"/>
+      <c r="DB54" s="21">
+        <v>15.762783594215666</v>
+      </c>
       <c r="DC54" s="23"/>
       <c r="DD54" s="23"/>
       <c r="DE54" s="23"/>
@@ -13971,7 +14048,9 @@
       <c r="DA55" s="21">
         <v>19.481497300648474</v>
       </c>
-      <c r="DB55" s="21"/>
+      <c r="DB55" s="21">
+        <v>21.057039530382511</v>
+      </c>
       <c r="DC55" s="23"/>
       <c r="DD55" s="23"/>
       <c r="DE55" s="23"/>
@@ -14298,7 +14377,9 @@
       <c r="DA56" s="21">
         <v>76.432544260990852</v>
       </c>
-      <c r="DB56" s="21"/>
+      <c r="DB56" s="21">
+        <v>78.640884091170875</v>
+      </c>
       <c r="DC56" s="23"/>
       <c r="DD56" s="23"/>
       <c r="DE56" s="23"/>
@@ -14625,7 +14706,9 @@
       <c r="DA57" s="21">
         <v>17.645104751930347</v>
       </c>
-      <c r="DB57" s="21"/>
+      <c r="DB57" s="21">
+        <v>16.950427788526774</v>
+      </c>
       <c r="DC57" s="23"/>
       <c r="DD57" s="23"/>
       <c r="DE57" s="23"/>
@@ -14952,7 +15035,9 @@
       <c r="DA58" s="25">
         <v>2.9643463212406553</v>
       </c>
-      <c r="DB58" s="25"/>
+      <c r="DB58" s="25">
+        <v>10.634728120671232</v>
+      </c>
       <c r="DC58" s="23"/>
       <c r="DD58" s="23"/>
       <c r="DE58" s="23"/>
@@ -15069,13 +15154,14 @@
       <c r="CY59" s="15"/>
       <c r="CZ59" s="15"/>
       <c r="DA59" s="15"/>
+      <c r="DB59" s="15"/>
     </row>
     <row r="60" spans="1:115" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="1048576" spans="94:105" x14ac:dyDescent="0.2">
+    <row r="1048576" spans="94:106" x14ac:dyDescent="0.2">
       <c r="CP1048576" s="18"/>
       <c r="CQ1048576" s="18"/>
       <c r="CR1048576" s="18"/>
@@ -15088,6 +15174,7 @@
       <c r="CY1048576" s="21"/>
       <c r="CZ1048576" s="21"/>
       <c r="DA1048576" s="21"/>
+      <c r="DB1048576" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
